--- a/registration_forms/038_hackathon_attendance_form--registration_forms.xlsx
+++ b/registration_forms/038_hackathon_attendance_form--registration_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -892,12 +892,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>participant_name</t>
+          <t>participant_name_2</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>participant_name</t>
+          <t>Participant Name 2</t>
         </is>
       </c>
       <c r="D20" t="inlineStr"/>
@@ -938,12 +938,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>participant_status</t>
+          <t>participant_status_2</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>participant_status</t>
+          <t>Participant Status 2</t>
         </is>
       </c>
       <c r="D22" t="inlineStr"/>
@@ -961,12 +961,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>hackathon</t>
+          <t>hackathon_2</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>hackathon</t>
+          <t>Hackathon 2</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -988,12 +988,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>role</t>
+          <t>role_2</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>role</t>
+          <t>Role 2</t>
         </is>
       </c>
       <c r="D24" t="inlineStr"/>
@@ -1011,12 +1011,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>team</t>
+          <t>team_2</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>team</t>
+          <t>Team 2</t>
         </is>
       </c>
       <c r="D25" t="inlineStr"/>
@@ -1034,12 +1034,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>team_members</t>
+          <t>team_members_2</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>team_members</t>
+          <t>Team Members 2</t>
         </is>
       </c>
       <c r="D26" t="inlineStr"/>
@@ -1057,12 +1057,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>participant_name</t>
+          <t>participant_name_3</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>participant_name</t>
+          <t>Participant Name 3</t>
         </is>
       </c>
       <c r="D27" t="inlineStr"/>
@@ -1080,12 +1080,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>notes</t>
+          <t>notes_2</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>notes</t>
+          <t>Notes 2</t>
         </is>
       </c>
       <c r="D28" t="inlineStr"/>
@@ -1109,7 +1109,7 @@
   <dimension ref="A1:C7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="28" customWidth="1" min="1" max="1"/>
+    <col width="30" customWidth="1" min="1" max="1"/>
     <col width="10" customWidth="1" min="2" max="2"/>
     <col width="10" customWidth="1" min="3" max="3"/>
   </cols>
@@ -1185,7 +1185,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>participant_status_choices</t>
+          <t>participant_status_2_choices</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -1202,7 +1202,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>participant_status_choices</t>
+          <t>participant_status_2_choices</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1219,7 +1219,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>participant_status_choices</t>
+          <t>participant_status_2_choices</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
